--- a/Файлы/1 курс/2 семестр/Теоретическая информатика/Лабы/26.03.25 - Лаба №4/Влад/4 лаба.xlsx
+++ b/Файлы/1 курс/2 семестр/Теоретическая информатика/Лабы/26.03.25 - Лаба №4/Влад/4 лаба.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="14400" windowHeight="15600" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="14400" windowHeight="15600" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Исходная таблица" sheetId="1" r:id="rId1"/>
@@ -21,9 +21,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Задание 4'!$A$1:$G$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Задание 5'!$A$1:$G$16</definedName>
     <definedName name="_xlnm.Extract" localSheetId="2">'Задание 4'!$A$18:$G$18</definedName>
-    <definedName name="_xlnm.Extract" localSheetId="3">'Задание 5'!$O$1:$U$1</definedName>
+    <definedName name="_xlnm.Extract" localSheetId="3">'Задание 5'!$A$71:$G$71</definedName>
     <definedName name="_xlnm.Criteria" localSheetId="2">'Задание 4'!#REF!</definedName>
-    <definedName name="_xlnm.Criteria" localSheetId="3">'Задание 5'!$A$33:$G$35</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="3">'Задание 5'!$A$67:$G$68</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="25">
   <si>
     <t xml:space="preserve">Ведомость учёта заказов </t>
   </si>
@@ -97,10 +97,19 @@
     <t>Тостер</t>
   </si>
   <si>
-    <t>&gt; 01.04.2014</t>
+    <t>&gt;15</t>
   </si>
   <si>
-    <t>&lt; 30.04.2014</t>
+    <t>Седова</t>
+  </si>
+  <si>
+    <t>&gt;2000</t>
+  </si>
+  <si>
+    <t>&lt;1000</t>
+  </si>
+  <si>
+    <t>&gt;1/4/2014</t>
   </si>
 </sst>
 </file>
@@ -133,7 +142,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -156,25 +165,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -468,15 +504,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -869,15 +905,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3074,16 +3110,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X35"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:X78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" customWidth="1"/>
     <col min="6" max="6" width="13.5703125" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3109,18 +3147,13 @@
       <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="4"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -3144,18 +3177,13 @@
       <c r="G2" s="2">
         <v>37200</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -3179,18 +3207,18 @@
       <c r="G3" s="2">
         <v>21000</v>
       </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -3214,18 +3242,13 @@
       <c r="G4" s="2">
         <v>6000</v>
       </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -3249,18 +3272,13 @@
       <c r="G5" s="2">
         <v>10800</v>
       </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
@@ -3284,18 +3302,13 @@
       <c r="G6" s="2">
         <v>49600</v>
       </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
@@ -3319,18 +3332,13 @@
       <c r="G7" s="2">
         <v>21000</v>
       </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
@@ -3423,18 +3431,18 @@
       <c r="G11" s="2">
         <v>46000</v>
       </c>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
@@ -3458,18 +3466,18 @@
       <c r="G12" s="2">
         <v>31000</v>
       </c>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
@@ -3493,18 +3501,18 @@
       <c r="G13" s="2">
         <v>7200</v>
       </c>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="5"/>
-      <c r="X13" s="5"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -3528,18 +3536,18 @@
       <c r="G14" s="2">
         <v>12000</v>
       </c>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+      <c r="X14" s="4"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -3563,18 +3571,18 @@
       <c r="G15" s="2">
         <v>84000</v>
       </c>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
-      <c r="X15" s="5"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="4"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -3598,204 +3606,212 @@
       <c r="G16" s="2">
         <v>7600</v>
       </c>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="5"/>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5"/>
-      <c r="X16" s="5"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="5"/>
-      <c r="U17" s="5"/>
-      <c r="V17" s="5"/>
-      <c r="W17" s="5"/>
-      <c r="X17" s="5"/>
-    </row>
-    <row r="18" spans="1:24" ht="60" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+      <c r="X16" s="4"/>
+    </row>
+    <row r="17" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+    </row>
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="8"/>
+      <c r="C18" s="10"/>
+      <c r="S18" s="10"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="6"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+    </row>
+    <row r="20" spans="1:24" ht="60" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5"/>
-      <c r="X18" s="5"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="3">
-        <v>41739</v>
-      </c>
-      <c r="D19" s="2">
-        <v>18</v>
-      </c>
-      <c r="E19" s="2">
-        <v>16</v>
-      </c>
-      <c r="F19" s="2">
-        <v>3100</v>
-      </c>
-      <c r="G19" s="2">
-        <v>49600</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="3">
-        <v>41786</v>
-      </c>
-      <c r="D20" s="2">
-        <v>16</v>
-      </c>
-      <c r="E20" s="2">
-        <v>20</v>
-      </c>
-      <c r="F20" s="2">
-        <v>2300</v>
-      </c>
-      <c r="G20" s="2">
-        <v>46000</v>
-      </c>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+      <c r="X20" s="4"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="3">
-        <v>41793</v>
-      </c>
-      <c r="D21" s="2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="2">
-        <v>20</v>
-      </c>
-      <c r="F21" s="2">
-        <v>4200</v>
-      </c>
-      <c r="G21" s="2">
-        <v>84000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" ht="60" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="G21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="6"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+      <c r="X21" s="4"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
+      <c r="X22" s="4"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
+      <c r="X23" s="4"/>
+    </row>
+    <row r="24" spans="1:24" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G24" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="3">
-        <v>41755</v>
-      </c>
-      <c r="D24" s="2">
-        <v>10</v>
-      </c>
-      <c r="E24" s="2">
-        <v>10</v>
-      </c>
-      <c r="F24" s="2">
-        <v>600</v>
-      </c>
-      <c r="G24" s="2">
-        <v>6000</v>
-      </c>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C25" s="3">
-        <v>41770</v>
+        <v>41739</v>
       </c>
       <c r="D25" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E25" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>600</v>
+        <v>3100</v>
       </c>
       <c r="G25" s="2">
-        <v>10800</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
@@ -3803,178 +3819,878 @@
         <v>10</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C26" s="3">
-        <v>41739</v>
+        <v>41786</v>
       </c>
       <c r="D26" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E26" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F26" s="2">
-        <v>3100</v>
+        <v>2300</v>
       </c>
       <c r="G26" s="2">
-        <v>49600</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="3">
+        <v>41793</v>
+      </c>
+      <c r="D27" s="2">
+        <v>22</v>
+      </c>
+      <c r="E27" s="2">
+        <v>20</v>
+      </c>
+      <c r="F27" s="2">
+        <v>4200</v>
+      </c>
+      <c r="G27" s="2">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8"/>
+      <c r="C29" s="10"/>
+    </row>
+    <row r="30" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="6"/>
+    </row>
+    <row r="31" spans="1:24" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32"/>
+      <c r="B32"/>
+      <c r="D32" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33"/>
+      <c r="B33"/>
+      <c r="F33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="3">
+        <v>41755</v>
+      </c>
+      <c r="D36" s="2">
+        <v>10</v>
+      </c>
+      <c r="E36" s="2">
+        <v>10</v>
+      </c>
+      <c r="F36" s="2">
+        <v>600</v>
+      </c>
+      <c r="G36" s="2">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="3">
+        <v>41770</v>
+      </c>
+      <c r="D37" s="2">
         <v>15</v>
       </c>
-      <c r="C27" s="3">
+      <c r="E37" s="2">
+        <v>18</v>
+      </c>
+      <c r="F37" s="2">
+        <v>600</v>
+      </c>
+      <c r="G37" s="2">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="3">
+        <v>41739</v>
+      </c>
+      <c r="D38" s="2">
+        <v>18</v>
+      </c>
+      <c r="E38" s="2">
+        <v>16</v>
+      </c>
+      <c r="F38" s="2">
+        <v>3100</v>
+      </c>
+      <c r="G38" s="2">
+        <v>49600</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="3">
         <v>41775</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D39" s="2">
         <v>24</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E39" s="2">
         <v>24</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F39" s="2">
         <v>2100</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G39" s="2">
         <v>50400</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="2" t="s">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C40" s="3">
         <v>41786</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D40" s="2">
         <v>16</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E40" s="2">
         <v>20</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F40" s="2">
         <v>2300</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G40" s="2">
         <v>46000</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="2" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C41" s="3">
         <v>41788</v>
       </c>
-      <c r="D29" s="2">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2">
-        <v>8</v>
-      </c>
-      <c r="F29" s="2">
+      <c r="D41" s="2">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2">
+        <v>8</v>
+      </c>
+      <c r="F41" s="2">
         <v>900</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G41" s="2">
         <v>7200</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B30" s="2" t="s">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C42" s="3">
         <v>41793</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D42" s="2">
         <v>22</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E42" s="2">
         <v>20</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F42" s="2">
         <v>4200</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G42" s="2">
         <v>84000</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="2" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C43" s="3">
         <v>41751</v>
       </c>
-      <c r="D31" s="2">
-        <v>10</v>
-      </c>
-      <c r="E31" s="2">
-        <v>8</v>
-      </c>
-      <c r="F31" s="2">
+      <c r="D43" s="2">
+        <v>10</v>
+      </c>
+      <c r="E43" s="2">
+        <v>8</v>
+      </c>
+      <c r="F43" s="2">
         <v>950</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G43" s="2">
         <v>7600</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+    <row r="44" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+    </row>
+    <row r="45" spans="1:7" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="8"/>
+      <c r="C45" s="10"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+    </row>
+    <row r="47" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G47" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="3" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="G49" s="4"/>
+    </row>
+    <row r="50" spans="1:24" ht="60" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="3">
+        <v>41739</v>
+      </c>
+      <c r="D51" s="2">
+        <v>18</v>
+      </c>
+      <c r="E51" s="2">
+        <v>16</v>
+      </c>
+      <c r="F51" s="2">
+        <v>3100</v>
+      </c>
+      <c r="G51" s="2">
+        <v>49600</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="3">
+        <v>41735</v>
+      </c>
+      <c r="D52" s="2">
+        <v>10</v>
+      </c>
+      <c r="E52" s="2">
+        <v>10</v>
+      </c>
+      <c r="F52" s="2">
+        <v>3100</v>
+      </c>
+      <c r="G52" s="2">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+    </row>
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="8"/>
+      <c r="C54" s="10"/>
+    </row>
+    <row r="56" spans="1:24" ht="60" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="D57" t="b">
+        <f>D2&gt;E2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" ht="60" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C60" s="3">
+        <v>41751</v>
+      </c>
+      <c r="D60" s="2">
+        <v>10</v>
+      </c>
+      <c r="E60" s="2">
+        <v>8</v>
+      </c>
+      <c r="F60" s="2">
+        <v>950</v>
+      </c>
+      <c r="G60" s="2">
+        <v>7600</v>
+      </c>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="4"/>
+      <c r="S60" s="6"/>
+      <c r="T60" s="4"/>
+      <c r="U60" s="4"/>
+      <c r="V60" s="4"/>
+      <c r="W60" s="4"/>
+      <c r="X60" s="4"/>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="3">
+        <v>41776</v>
+      </c>
+      <c r="D61" s="2">
+        <v>12</v>
+      </c>
+      <c r="E61" s="2">
+        <v>10</v>
+      </c>
+      <c r="F61" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G61" s="2">
+        <v>12000</v>
+      </c>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4"/>
+      <c r="T61" s="4"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="4"/>
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" s="3">
+        <v>41739</v>
+      </c>
+      <c r="D62" s="2">
+        <v>18</v>
+      </c>
+      <c r="E62" s="2">
+        <v>16</v>
+      </c>
+      <c r="F62" s="2">
+        <v>3100</v>
+      </c>
+      <c r="G62" s="2">
+        <v>49600</v>
+      </c>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="4"/>
+      <c r="S62" s="4"/>
+      <c r="T62" s="4"/>
+      <c r="U62" s="4"/>
+      <c r="V62" s="4"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="3">
+        <v>41793</v>
+      </c>
+      <c r="D63" s="2">
+        <v>22</v>
+      </c>
+      <c r="E63" s="2">
         <v>20</v>
       </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C35" s="3" t="s">
-        <v>21</v>
+      <c r="F63" s="2">
+        <v>4200</v>
+      </c>
+      <c r="G63" s="2">
+        <v>84000</v>
+      </c>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="5"/>
+      <c r="R63" s="5"/>
+      <c r="S63" s="5"/>
+      <c r="T63" s="5"/>
+      <c r="U63" s="5"/>
+      <c r="V63" s="5"/>
+      <c r="W63" s="5"/>
+      <c r="X63" s="4"/>
+    </row>
+    <row r="64" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="1:24" s="9" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="8"/>
+    </row>
+    <row r="67" spans="1:24" ht="60" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C69" t="b">
+        <f>AND(M2&gt;15/5/2014,M2&lt;=31/5/2014)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" ht="60" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="3">
+        <v>41739</v>
+      </c>
+      <c r="D72" s="2">
+        <v>18</v>
+      </c>
+      <c r="E72" s="2">
+        <v>16</v>
+      </c>
+      <c r="F72" s="2">
+        <v>3100</v>
+      </c>
+      <c r="G72" s="2">
+        <v>49600</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="3">
+        <v>41775</v>
+      </c>
+      <c r="D73" s="2">
+        <v>24</v>
+      </c>
+      <c r="E73" s="2">
+        <v>24</v>
+      </c>
+      <c r="F73" s="2">
+        <v>2100</v>
+      </c>
+      <c r="G73" s="2">
+        <v>50400</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="3">
+        <v>41786</v>
+      </c>
+      <c r="D74" s="2">
+        <v>16</v>
+      </c>
+      <c r="E74" s="2">
+        <v>20</v>
+      </c>
+      <c r="F74" s="2">
+        <v>2300</v>
+      </c>
+      <c r="G74" s="2">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C75" s="3">
+        <v>41793</v>
+      </c>
+      <c r="D75" s="2">
+        <v>22</v>
+      </c>
+      <c r="E75" s="2">
+        <v>20</v>
+      </c>
+      <c r="F75" s="2">
+        <v>4200</v>
+      </c>
+      <c r="G75" s="2">
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="3">
+        <v>41783</v>
+      </c>
+      <c r="D76" s="2">
+        <v>12</v>
+      </c>
+      <c r="E76" s="2">
+        <v>12</v>
+      </c>
+      <c r="F76" s="2">
+        <v>3100</v>
+      </c>
+      <c r="G76" s="2">
+        <v>37200</v>
+      </c>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4"/>
+      <c r="R76" s="4"/>
+      <c r="S76" s="4"/>
+      <c r="T76" s="4"/>
+      <c r="U76" s="4"/>
+      <c r="V76" s="4"/>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" s="3">
+        <v>41776</v>
+      </c>
+      <c r="D77" s="2">
+        <v>12</v>
+      </c>
+      <c r="E77" s="2">
+        <v>10</v>
+      </c>
+      <c r="F77" s="2">
+        <v>1200</v>
+      </c>
+      <c r="G77" s="2">
+        <v>12000</v>
+      </c>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="4"/>
+      <c r="S77" s="4"/>
+      <c r="T77" s="4"/>
+      <c r="U77" s="4"/>
+      <c r="V77" s="4"/>
+      <c r="W77" s="4"/>
+      <c r="X77" s="4"/>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" s="3">
+        <v>41788</v>
+      </c>
+      <c r="D78" s="2">
+        <v>8</v>
+      </c>
+      <c r="E78" s="2">
+        <v>8</v>
+      </c>
+      <c r="F78" s="2">
+        <v>900</v>
+      </c>
+      <c r="G78" s="2">
+        <v>7200</v>
       </c>
     </row>
   </sheetData>
